--- a/vulnerability/lighttpd1_漏洞发现_20260607230915.xlsx
+++ b/vulnerability/lighttpd1_漏洞发现_20260607230915.xlsx
@@ -125,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -160,6 +160,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -526,7 +529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J126"/>
+  <dimension ref="A1:K126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -539,6 +542,7 @@
     <col width="70" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
     <col width="62" customWidth="1" min="10" max="10"/>
+    <col width="65" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -547,6 +551,7 @@
           <t>ChatAFL-Opt Fuzzing -- lighttpd1 HTTP协议漏洞发现清单 (123条记录, 10组实验, 0个Crash)</t>
         </is>
       </c>
+      <c r="K1" s="1" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -554,6 +559,7 @@
           <t>数据源: results-lighttpd1_ablation_full_20260531T154724 | 生成: 2026-06-07 23:09:15 | 总执行~5300万次 | Crash:0 | 原始种子:123 | 去重:123</t>
         </is>
       </c>
+      <c r="K2" s="13" t="n"/>
     </row>
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
@@ -604,6 +610,11 @@
       <c r="J3" s="3" t="inlineStr">
         <is>
           <t>为什么算漏洞</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>漏洞带来的影响</t>
         </is>
       </c>
     </row>
@@ -763,6 +774,14 @@
           <t>多个Content-Length头违反RFC 7230。前后端对请求体边界解析不一致导致HTTP走私攻击。10/10组均发现。</t>
         </is>
       </c>
+      <c r="K4" s="13" t="inlineStr">
+        <is>
+          <t>【HTTP缓存投毒】攻击者可利用lighttpd的HTTP请求走私/响应分割漏洞，向前端缓存/代理服务器注入恶意HTTP响应，污染缓存内容。后续合法用户请求将收到被篡改的缓存内容，可能导致XSS、恶意重定向或恶意文件下载。
+【会话劫持与凭证窃取】通过HTTP响应头注入，攻击者可构造恶意响应设置Cookie、重定向用户到钓鱼页面，或注入恶意JavaScript代码窃取用户会话令牌和登录凭证。
+【WAF/安全设备绕过】前端代理与后端lighttpd对HTTP请求边界解析不一致，允许恶意请求绕过Web应用防火墙(WAF)的检测规则，直接到达后端服务器。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="260" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
@@ -854,6 +873,14 @@
           <t>GET /../hello.txt返回200 OK, body='HELLO WORLD!!'。绕过Web根目录限制,泄露上级目录文件。该版本路径规范化存在缺陷。</t>
         </is>
       </c>
+      <c r="K5" s="13" t="inlineStr">
+        <is>
+          <t>【敏感文件读取】攻击者可利用lighttpd的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若lighttpd为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="260" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -954,6 +981,14 @@
       <c r="J6" s="4" t="inlineStr">
         <is>
           <t>多个Content-Length头违反RFC 7230。前后端对请求体边界解析不一致导致HTTP走私攻击。10/10组均发现。</t>
+        </is>
+      </c>
+      <c r="K6" s="13" t="inlineStr">
+        <is>
+          <t>【HTTP缓存投毒】攻击者可利用lighttpd的HTTP请求走私/响应分割漏洞，向前端缓存/代理服务器注入恶意HTTP响应，污染缓存内容。后续合法用户请求将收到被篡改的缓存内容，可能导致XSS、恶意重定向或恶意文件下载。
+【会话劫持与凭证窃取】通过HTTP响应头注入，攻击者可构造恶意响应设置Cookie、重定向用户到钓鱼页面，或注入恶意JavaScript代码窃取用户会话令牌和登录凭证。
+【WAF/安全设备绕过】前端代理与后端lighttpd对HTTP请求边界解析不一致，允许恶意请求绕过Web应用防火墙(WAF)的检测规则，直接到达后端服务器。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -1050,6 +1085,14 @@
       <c r="J7" s="5" t="inlineStr">
         <is>
           <t>GET /../hello.txt返回200 OK, body='HELLO WORLD!!'。绕过Web根目录限制,泄露上级目录文件。该版本路径规范化存在缺陷。</t>
+        </is>
+      </c>
+      <c r="K7" s="13" t="inlineStr">
+        <is>
+          <t>【敏感文件读取】攻击者可利用lighttpd的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若lighttpd为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -1283,6 +1326,14 @@
           <t>多个Content-Length头违反RFC 7230。前后端对请求体边界解析不一致导致HTTP走私攻击。10/10组均发现。</t>
         </is>
       </c>
+      <c r="K8" s="13" t="inlineStr">
+        <is>
+          <t>【HTTP缓存投毒】攻击者可利用lighttpd的HTTP请求走私/响应分割漏洞，向前端缓存/代理服务器注入恶意HTTP响应，污染缓存内容。后续合法用户请求将收到被篡改的缓存内容，可能导致XSS、恶意重定向或恶意文件下载。
+【会话劫持与凭证窃取】通过HTTP响应头注入，攻击者可构造恶意响应设置Cookie、重定向用户到钓鱼页面，或注入恶意JavaScript代码窃取用户会话令牌和登录凭证。
+【WAF/安全设备绕过】前端代理与后端lighttpd对HTTP请求边界解析不一致，允许恶意请求绕过Web应用防火墙(WAF)的检测规则，直接到达后端服务器。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="260" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
@@ -1531,6 +1582,14 @@
           <t>GET /../hello.txt返回200 OK, body='HELLO WORLD!!'。绕过Web根目录限制,泄露上级目录文件。该版本路径规范化存在缺陷。</t>
         </is>
       </c>
+      <c r="K9" s="13" t="inlineStr">
+        <is>
+          <t>【敏感文件读取】攻击者可利用lighttpd的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若lighttpd为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="260" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
@@ -1821,6 +1880,14 @@
           <t>多个Content-Length头违反RFC 7230。前后端对请求体边界解析不一致导致HTTP走私攻击。10/10组均发现。</t>
         </is>
       </c>
+      <c r="K10" s="13" t="inlineStr">
+        <is>
+          <t>【HTTP缓存投毒】攻击者可利用lighttpd的HTTP请求走私/响应分割漏洞，向前端缓存/代理服务器注入恶意HTTP响应，污染缓存内容。后续合法用户请求将收到被篡改的缓存内容，可能导致XSS、恶意重定向或恶意文件下载。
+【会话劫持与凭证窃取】通过HTTP响应头注入，攻击者可构造恶意响应设置Cookie、重定向用户到钓鱼页面，或注入恶意JavaScript代码窃取用户会话令牌和登录凭证。
+【WAF/安全设备绕过】前端代理与后端lighttpd对HTTP请求边界解析不一致，允许恶意请求绕过Web应用防火墙(WAF)的检测规则，直接到达后端服务器。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="260" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
@@ -1929,6 +1996,14 @@
           <t>Content-Length与Transfer-Encoding同时存在,违反RFC 7230。前后端解析差异可致HTTP走私/缓存投毒/请求劫持。</t>
         </is>
       </c>
+      <c r="K11" s="13" t="inlineStr">
+        <is>
+          <t>【HTTP缓存投毒】攻击者可利用lighttpd的HTTP请求走私/响应分割漏洞，向前端缓存/代理服务器注入恶意HTTP响应，污染缓存内容。后续合法用户请求将收到被篡改的缓存内容，可能导致XSS、恶意重定向或恶意文件下载。
+【会话劫持与凭证窃取】通过HTTP响应头注入，攻击者可构造恶意响应设置Cookie、重定向用户到钓鱼页面，或注入恶意JavaScript代码窃取用户会话令牌和登录凭证。
+【WAF/安全设备绕过】前端代理与后端lighttpd对HTTP请求边界解析不一致，允许恶意请求绕过Web应用防火墙(WAF)的检测规则，直接到达后端服务器。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="260" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
@@ -2012,6 +2087,14 @@
       <c r="J12" s="5" t="inlineStr">
         <is>
           <t>GET /../hello.txt返回200 OK, body='HELLO WORLD!!'。绕过Web根目录限制,泄露上级目录文件。该版本路径规范化存在缺陷。</t>
+        </is>
+      </c>
+      <c r="K12" s="13" t="inlineStr">
+        <is>
+          <t>【敏感文件读取】攻击者可利用lighttpd的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若lighttpd为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -2119,6 +2202,14 @@
           <t>Content-Length与Transfer-Encoding同时存在,违反RFC 7230。前后端解析差异可致HTTP走私/缓存投毒/请求劫持。</t>
         </is>
       </c>
+      <c r="K13" s="13" t="inlineStr">
+        <is>
+          <t>【HTTP缓存投毒】攻击者可利用lighttpd的HTTP请求走私/响应分割漏洞，向前端缓存/代理服务器注入恶意HTTP响应，污染缓存内容。后续合法用户请求将收到被篡改的缓存内容，可能导致XSS、恶意重定向或恶意文件下载。
+【会话劫持与凭证窃取】通过HTTP响应头注入，攻击者可构造恶意响应设置Cookie、重定向用户到钓鱼页面，或注入恶意JavaScript代码窃取用户会话令牌和登录凭证。
+【WAF/安全设备绕过】前端代理与后端lighttpd对HTTP请求边界解析不一致，允许恶意请求绕过Web应用防火墙(WAF)的检测规则，直接到达后端服务器。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="260" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
@@ -2209,6 +2300,14 @@
           <t>GET /../hello.txt返回200 OK, body='HELLO WORLD!!'。绕过Web根目录限制,泄露上级目录文件。该版本路径规范化存在缺陷。</t>
         </is>
       </c>
+      <c r="K14" s="13" t="inlineStr">
+        <is>
+          <t>【敏感文件读取】攻击者可利用lighttpd的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若lighttpd为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="260" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
@@ -2305,6 +2404,14 @@
           <t>多个Content-Length头违反RFC 7230。前后端对请求体边界解析不一致导致HTTP走私攻击。10/10组均发现。</t>
         </is>
       </c>
+      <c r="K15" s="13" t="inlineStr">
+        <is>
+          <t>【HTTP缓存投毒】攻击者可利用lighttpd的HTTP请求走私/响应分割漏洞，向前端缓存/代理服务器注入恶意HTTP响应，污染缓存内容。后续合法用户请求将收到被篡改的缓存内容，可能导致XSS、恶意重定向或恶意文件下载。
+【会话劫持与凭证窃取】通过HTTP响应头注入，攻击者可构造恶意响应设置Cookie、重定向用户到钓鱼页面，或注入恶意JavaScript代码窃取用户会话令牌和登录凭证。
+【WAF/安全设备绕过】前端代理与后端lighttpd对HTTP请求边界解析不一致，允许恶意请求绕过Web应用防火墙(WAF)的检测规则，直接到达后端服务器。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="260" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
@@ -2411,6 +2518,14 @@
           <t>GET /../hello.txt返回200 OK, body='HELLO WORLD!!'。绕过Web根目录限制,泄露上级目录文件。该版本路径规范化存在缺陷。</t>
         </is>
       </c>
+      <c r="K16" s="13" t="inlineStr">
+        <is>
+          <t>【敏感文件读取】攻击者可利用lighttpd的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若lighttpd为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="260" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
@@ -2507,6 +2622,14 @@
       <c r="J17" s="4" t="inlineStr">
         <is>
           <t>多个Content-Length头违反RFC 7230。前后端对请求体边界解析不一致导致HTTP走私攻击。10/10组均发现。</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="inlineStr">
+        <is>
+          <t>【HTTP缓存投毒】攻击者可利用lighttpd的HTTP请求走私/响应分割漏洞，向前端缓存/代理服务器注入恶意HTTP响应，污染缓存内容。后续合法用户请求将收到被篡改的缓存内容，可能导致XSS、恶意重定向或恶意文件下载。
+【会话劫持与凭证窃取】通过HTTP响应头注入，攻击者可构造恶意响应设置Cookie、重定向用户到钓鱼页面，或注入恶意JavaScript代码窃取用户会话令牌和登录凭证。
+【WAF/安全设备绕过】前端代理与后端lighttpd对HTTP请求边界解析不一致，允许恶意请求绕过Web应用防火墙(WAF)的检测规则，直接到达后端服务器。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -2604,6 +2727,14 @@
           <t>GET /../hello.txt返回200 OK, body='HELLO WORLD!!'。绕过Web根目录限制,泄露上级目录文件。该版本路径规范化存在缺陷。</t>
         </is>
       </c>
+      <c r="K18" s="13" t="inlineStr">
+        <is>
+          <t>【敏感文件读取】攻击者可利用lighttpd的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若lighttpd为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="260" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
@@ -2777,6 +2908,14 @@
           <t>Content-Length与Transfer-Encoding同时存在,违反RFC 7230。前后端解析差异可致HTTP走私/缓存投毒/请求劫持。</t>
         </is>
       </c>
+      <c r="K19" s="13" t="inlineStr">
+        <is>
+          <t>【HTTP缓存投毒】攻击者可利用lighttpd的HTTP请求走私/响应分割漏洞，向前端缓存/代理服务器注入恶意HTTP响应，污染缓存内容。后续合法用户请求将收到被篡改的缓存内容，可能导致XSS、恶意重定向或恶意文件下载。
+【会话劫持与凭证窃取】通过HTTP响应头注入，攻击者可构造恶意响应设置Cookie、重定向用户到钓鱼页面，或注入恶意JavaScript代码窃取用户会话令牌和登录凭证。
+【WAF/安全设备绕过】前端代理与后端lighttpd对HTTP请求边界解析不一致，允许恶意请求绕过Web应用防火墙(WAF)的检测规则，直接到达后端服务器。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="260" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
@@ -2877,6 +3016,14 @@
       <c r="J20" s="5" t="inlineStr">
         <is>
           <t>GET /../hello.txt返回200 OK, body='HELLO WORLD!!'。绕过Web根目录限制,泄露上级目录文件。该版本路径规范化存在缺陷。</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="inlineStr">
+        <is>
+          <t>【敏感文件读取】攻击者可利用lighttpd的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若lighttpd为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -3131,6 +3278,14 @@
           <t>GET /../hello.txt返回200 OK, body='HELLO WORLD!!'。绕过Web根目录限制,泄露上级目录文件。该版本路径规范化存在缺陷。</t>
         </is>
       </c>
+      <c r="K21" s="13" t="inlineStr">
+        <is>
+          <t>【敏感文件读取】攻击者可利用lighttpd的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若lighttpd为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="260" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
@@ -3272,6 +3427,14 @@
       <c r="J22" s="4" t="inlineStr">
         <is>
           <t>Content-Length与Transfer-Encoding同时存在,违反RFC 7230。前后端解析差异可致HTTP走私/缓存投毒/请求劫持。</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="inlineStr">
+        <is>
+          <t>【HTTP缓存投毒】攻击者可利用lighttpd的HTTP请求走私/响应分割漏洞，向前端缓存/代理服务器注入恶意HTTP响应，污染缓存内容。后续合法用户请求将收到被篡改的缓存内容，可能导致XSS、恶意重定向或恶意文件下载。
+【会话劫持与凭证窃取】通过HTTP响应头注入，攻击者可构造恶意响应设置Cookie、重定向用户到钓鱼页面，或注入恶意JavaScript代码窃取用户会话令牌和登录凭证。
+【WAF/安全设备绕过】前端代理与后端lighttpd对HTTP请求边界解析不一致，允许恶意请求绕过Web应用防火墙(WAF)的检测规则，直接到达后端服务器。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -3367,6 +3530,14 @@
           <t>GET /../hello.txt返回200 OK, body='HELLO WORLD!!'。绕过Web根目录限制,泄露上级目录文件。该版本路径规范化存在缺陷。</t>
         </is>
       </c>
+      <c r="K23" s="13" t="inlineStr">
+        <is>
+          <t>【敏感文件读取】攻击者可利用lighttpd的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若lighttpd为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="260" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
@@ -3455,6 +3626,14 @@
       <c r="J24" s="6" t="inlineStr">
         <is>
           <t>请求包含嵌入CRLF和完整HTTP响应行,可致响应拆分攻击,注入恶意内容/Set-Cookie。7/10组确认。</t>
+        </is>
+      </c>
+      <c r="K24" s="13" t="inlineStr">
+        <is>
+          <t>【HTTP缓存投毒】攻击者可利用lighttpd的HTTP请求走私/响应分割漏洞，向前端缓存/代理服务器注入恶意HTTP响应，污染缓存内容。后续合法用户请求将收到被篡改的缓存内容，可能导致XSS、恶意重定向或恶意文件下载。
+【会话劫持与凭证窃取】通过HTTP响应头注入，攻击者可构造恶意响应设置Cookie、重定向用户到钓鱼页面，或注入恶意JavaScript代码窃取用户会话令牌和登录凭证。
+【WAF/安全设备绕过】前端代理与后端lighttpd对HTTP请求边界解析不一致，允许恶意请求绕过Web应用防火墙(WAF)的检测规则，直接到达后端服务器。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -3676,6 +3855,14 @@
           <t>GET /../hello.txt返回200 OK, body='HELLO WORLD!!'。绕过Web根目录限制,泄露上级目录文件。该版本路径规范化存在缺陷。</t>
         </is>
       </c>
+      <c r="K25" s="13" t="inlineStr">
+        <is>
+          <t>【敏感文件读取】攻击者可利用lighttpd的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若lighttpd为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="260" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
@@ -3766,6 +3953,14 @@
       <c r="J26" s="5" t="inlineStr">
         <is>
           <t>双重URL编码(%2e%2e=..)绕过路径规范化。若CGI配置可RCE。Oracle标记Severity=5(最高)。</t>
+        </is>
+      </c>
+      <c r="K26" s="13" t="inlineStr">
+        <is>
+          <t>【敏感文件读取】攻击者可利用lighttpd的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若lighttpd为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -3909,6 +4104,14 @@
           <t>多个Content-Length头违反RFC 7230。前后端对请求体边界解析不一致导致HTTP走私攻击。10/10组均发现。</t>
         </is>
       </c>
+      <c r="K27" s="13" t="inlineStr">
+        <is>
+          <t>【HTTP缓存投毒】攻击者可利用lighttpd的HTTP请求走私/响应分割漏洞，向前端缓存/代理服务器注入恶意HTTP响应，污染缓存内容。后续合法用户请求将收到被篡改的缓存内容，可能导致XSS、恶意重定向或恶意文件下载。
+【会话劫持与凭证窃取】通过HTTP响应头注入，攻击者可构造恶意响应设置Cookie、重定向用户到钓鱼页面，或注入恶意JavaScript代码窃取用户会话令牌和登录凭证。
+【WAF/安全设备绕过】前端代理与后端lighttpd对HTTP请求边界解析不一致，允许恶意请求绕过Web应用防火墙(WAF)的检测规则，直接到达后端服务器。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="260" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
@@ -4119,6 +4322,14 @@
       <c r="J28" s="4" t="inlineStr">
         <is>
           <t>多个Content-Length头违反RFC 7230。前后端对请求体边界解析不一致导致HTTP走私攻击。10/10组均发现。</t>
+        </is>
+      </c>
+      <c r="K28" s="13" t="inlineStr">
+        <is>
+          <t>【HTTP缓存投毒】攻击者可利用lighttpd的HTTP请求走私/响应分割漏洞，向前端缓存/代理服务器注入恶意HTTP响应，污染缓存内容。后续合法用户请求将收到被篡改的缓存内容，可能导致XSS、恶意重定向或恶意文件下载。
+【会话劫持与凭证窃取】通过HTTP响应头注入，攻击者可构造恶意响应设置Cookie、重定向用户到钓鱼页面，或注入恶意JavaScript代码窃取用户会话令牌和登录凭证。
+【WAF/安全设备绕过】前端代理与后端lighttpd对HTTP请求边界解析不一致，允许恶意请求绕过Web应用防火墙(WAF)的检测规则，直接到达后端服务器。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -4233,6 +4444,14 @@
           <t>多个Content-Length头违反RFC 7230。前后端对请求体边界解析不一致导致HTTP走私攻击。10/10组均发现。</t>
         </is>
       </c>
+      <c r="K29" s="13" t="inlineStr">
+        <is>
+          <t>【HTTP缓存投毒】攻击者可利用lighttpd的HTTP请求走私/响应分割漏洞，向前端缓存/代理服务器注入恶意HTTP响应，污染缓存内容。后续合法用户请求将收到被篡改的缓存内容，可能导致XSS、恶意重定向或恶意文件下载。
+【会话劫持与凭证窃取】通过HTTP响应头注入，攻击者可构造恶意响应设置Cookie、重定向用户到钓鱼页面，或注入恶意JavaScript代码窃取用户会话令牌和登录凭证。
+【WAF/安全设备绕过】前端代理与后端lighttpd对HTTP请求边界解析不一致，允许恶意请求绕过Web应用防火墙(WAF)的检测规则，直接到达后端服务器。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="260" customHeight="1">
       <c r="A30" s="5" t="inlineStr">
@@ -4337,6 +4556,14 @@
       <c r="J30" s="5" t="inlineStr">
         <is>
           <t>GET /../hello.txt返回200 OK, body='HELLO WORLD!!'。绕过Web根目录限制,泄露上级目录文件。该版本路径规范化存在缺陷。</t>
+        </is>
+      </c>
+      <c r="K30" s="13" t="inlineStr">
+        <is>
+          <t>【敏感文件读取】攻击者可利用lighttpd的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若lighttpd为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -4543,6 +4770,14 @@
           <t>多个Content-Length头违反RFC 7230。前后端对请求体边界解析不一致导致HTTP走私攻击。10/10组均发现。</t>
         </is>
       </c>
+      <c r="K31" s="13" t="inlineStr">
+        <is>
+          <t>【HTTP缓存投毒】攻击者可利用lighttpd的HTTP请求走私/响应分割漏洞，向前端缓存/代理服务器注入恶意HTTP响应，污染缓存内容。后续合法用户请求将收到被篡改的缓存内容，可能导致XSS、恶意重定向或恶意文件下载。
+【会话劫持与凭证窃取】通过HTTP响应头注入，攻击者可构造恶意响应设置Cookie、重定向用户到钓鱼页面，或注入恶意JavaScript代码窃取用户会话令牌和登录凭证。
+【WAF/安全设备绕过】前端代理与后端lighttpd对HTTP请求边界解析不一致，允许恶意请求绕过Web应用防火墙(WAF)的检测规则，直接到达后端服务器。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="260" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
@@ -4644,6 +4879,14 @@
           <t>GET /../hello.txt返回200 OK, body='HELLO WORLD!!'。绕过Web根目录限制,泄露上级目录文件。该版本路径规范化存在缺陷。</t>
         </is>
       </c>
+      <c r="K32" s="13" t="inlineStr">
+        <is>
+          <t>【敏感文件读取】攻击者可利用lighttpd的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若lighttpd为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="260" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
@@ -4742,6 +4985,14 @@
           <t>请求包含嵌入CRLF和完整HTTP响应行,可致响应拆分攻击,注入恶意内容/Set-Cookie。7/10组确认。</t>
         </is>
       </c>
+      <c r="K33" s="13" t="inlineStr">
+        <is>
+          <t>【HTTP缓存投毒】攻击者可利用lighttpd的HTTP请求走私/响应分割漏洞，向前端缓存/代理服务器注入恶意HTTP响应，污染缓存内容。后续合法用户请求将收到被篡改的缓存内容，可能导致XSS、恶意重定向或恶意文件下载。
+【会话劫持与凭证窃取】通过HTTP响应头注入，攻击者可构造恶意响应设置Cookie、重定向用户到钓鱼页面，或注入恶意JavaScript代码窃取用户会话令牌和登录凭证。
+【WAF/安全设备绕过】前端代理与后端lighttpd对HTTP请求边界解析不一致，允许恶意请求绕过Web应用防火墙(WAF)的检测规则，直接到达后端服务器。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="260" customHeight="1">
       <c r="A34" s="5" t="inlineStr">
@@ -4891,6 +5142,14 @@
       <c r="J34" s="5" t="inlineStr">
         <is>
           <t>GET /../hello.txt返回200 OK, body='HELLO WORLD!!'。绕过Web根目录限制,泄露上级目录文件。该版本路径规范化存在缺陷。</t>
+        </is>
+      </c>
+      <c r="K34" s="13" t="inlineStr">
+        <is>
+          <t>【敏感文件读取】攻击者可利用lighttpd的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若lighttpd为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -4986,6 +5245,14 @@
       <c r="J35" s="5" t="inlineStr">
         <is>
           <t>GET /../hello.txt返回200 OK, body='HELLO WORLD!!'。绕过Web根目录限制,泄露上级目录文件。该版本路径规范化存在缺陷。</t>
+        </is>
+      </c>
+      <c r="K35" s="13" t="inlineStr">
+        <is>
+          <t>【敏感文件读取】攻击者可利用lighttpd的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若lighttpd为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -5085,6 +5352,14 @@
           <t>多个Content-Length头违反RFC 7230。前后端对请求体边界解析不一致导致HTTP走私攻击。10/10组均发现。</t>
         </is>
       </c>
+      <c r="K36" s="13" t="inlineStr">
+        <is>
+          <t>【HTTP缓存投毒】攻击者可利用lighttpd的HTTP请求走私/响应分割漏洞，向前端缓存/代理服务器注入恶意HTTP响应，污染缓存内容。后续合法用户请求将收到被篡改的缓存内容，可能导致XSS、恶意重定向或恶意文件下载。
+【会话劫持与凭证窃取】通过HTTP响应头注入，攻击者可构造恶意响应设置Cookie、重定向用户到钓鱼页面，或注入恶意JavaScript代码窃取用户会话令牌和登录凭证。
+【WAF/安全设备绕过】前端代理与后端lighttpd对HTTP请求边界解析不一致，允许恶意请求绕过Web应用防火墙(WAF)的检测规则，直接到达后端服务器。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="260" customHeight="1">
       <c r="A37" s="5" t="inlineStr">
@@ -5176,6 +5451,14 @@
           <t>GET /../hello.txt返回200 OK, body='HELLO WORLD!!'。绕过Web根目录限制,泄露上级目录文件。该版本路径规范化存在缺陷。</t>
         </is>
       </c>
+      <c r="K37" s="13" t="inlineStr">
+        <is>
+          <t>【敏感文件读取】攻击者可利用lighttpd的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若lighttpd为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="260" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
@@ -5282,6 +5565,14 @@
       <c r="J38" s="4" t="inlineStr">
         <is>
           <t>多个Content-Length头违反RFC 7230。前后端对请求体边界解析不一致导致HTTP走私攻击。10/10组均发现。</t>
+        </is>
+      </c>
+      <c r="K38" s="13" t="inlineStr">
+        <is>
+          <t>【HTTP缓存投毒】攻击者可利用lighttpd的HTTP请求走私/响应分割漏洞，向前端缓存/代理服务器注入恶意HTTP响应，污染缓存内容。后续合法用户请求将收到被篡改的缓存内容，可能导致XSS、恶意重定向或恶意文件下载。
+【会话劫持与凭证窃取】通过HTTP响应头注入，攻击者可构造恶意响应设置Cookie、重定向用户到钓鱼页面，或注入恶意JavaScript代码窃取用户会话令牌和登录凭证。
+【WAF/安全设备绕过】前端代理与后端lighttpd对HTTP请求边界解析不一致，允许恶意请求绕过Web应用防火墙(WAF)的检测规则，直接到达后端服务器。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -5433,6 +5724,14 @@
           <t>GET /../hello.txt返回200 OK, body='HELLO WORLD!!'。绕过Web根目录限制,泄露上级目录文件。该版本路径规范化存在缺陷。</t>
         </is>
       </c>
+      <c r="K39" s="13" t="inlineStr">
+        <is>
+          <t>【敏感文件读取】攻击者可利用lighttpd的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若lighttpd为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="260" customHeight="1">
       <c r="A40" s="6" t="inlineStr">
@@ -5527,6 +5826,14 @@
       <c r="J40" s="6" t="inlineStr">
         <is>
           <t>请求包含嵌入CRLF和完整HTTP响应行,可致响应拆分攻击,注入恶意内容/Set-Cookie。7/10组确认。</t>
+        </is>
+      </c>
+      <c r="K40" s="13" t="inlineStr">
+        <is>
+          <t>【HTTP缓存投毒】攻击者可利用lighttpd的HTTP请求走私/响应分割漏洞，向前端缓存/代理服务器注入恶意HTTP响应，污染缓存内容。后续合法用户请求将收到被篡改的缓存内容，可能导致XSS、恶意重定向或恶意文件下载。
+【会话劫持与凭证窃取】通过HTTP响应头注入，攻击者可构造恶意响应设置Cookie、重定向用户到钓鱼页面，或注入恶意JavaScript代码窃取用户会话令牌和登录凭证。
+【WAF/安全设备绕过】前端代理与后端lighttpd对HTTP请求边界解析不一致，允许恶意请求绕过Web应用防火墙(WAF)的检测规则，直接到达后端服务器。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -5618,6 +5925,14 @@
       <c r="J41" s="5" t="inlineStr">
         <is>
           <t>GET /../hello.txt返回200 OK, body='HELLO WORLD!!'。绕过Web根目录限制,泄露上级目录文件。该版本路径规范化存在缺陷。</t>
+        </is>
+      </c>
+      <c r="K41" s="13" t="inlineStr">
+        <is>
+          <t>【敏感文件读取】攻击者可利用lighttpd的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若lighttpd为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -5809,6 +6124,14 @@
           <t>多个Content-Length头违反RFC 7230。前后端对请求体边界解析不一致导致HTTP走私攻击。10/10组均发现。</t>
         </is>
       </c>
+      <c r="K42" s="13" t="inlineStr">
+        <is>
+          <t>【HTTP缓存投毒】攻击者可利用lighttpd的HTTP请求走私/响应分割漏洞，向前端缓存/代理服务器注入恶意HTTP响应，污染缓存内容。后续合法用户请求将收到被篡改的缓存内容，可能导致XSS、恶意重定向或恶意文件下载。
+【会话劫持与凭证窃取】通过HTTP响应头注入，攻击者可构造恶意响应设置Cookie、重定向用户到钓鱼页面，或注入恶意JavaScript代码窃取用户会话令牌和登录凭证。
+【WAF/安全设备绕过】前端代理与后端lighttpd对HTTP请求边界解析不一致，允许恶意请求绕过Web应用防火墙(WAF)的检测规则，直接到达后端服务器。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="260" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
@@ -5912,6 +6235,14 @@
       <c r="J43" s="4" t="inlineStr">
         <is>
           <t>多个Content-Length头违反RFC 7230。前后端对请求体边界解析不一致导致HTTP走私攻击。10/10组均发现。</t>
+        </is>
+      </c>
+      <c r="K43" s="13" t="inlineStr">
+        <is>
+          <t>【HTTP缓存投毒】攻击者可利用lighttpd的HTTP请求走私/响应分割漏洞，向前端缓存/代理服务器注入恶意HTTP响应，污染缓存内容。后续合法用户请求将收到被篡改的缓存内容，可能导致XSS、恶意重定向或恶意文件下载。
+【会话劫持与凭证窃取】通过HTTP响应头注入，攻击者可构造恶意响应设置Cookie、重定向用户到钓鱼页面，或注入恶意JavaScript代码窃取用户会话令牌和登录凭证。
+【WAF/安全设备绕过】前端代理与后端lighttpd对HTTP请求边界解析不一致，允许恶意请求绕过Web应用防火墙(WAF)的检测规则，直接到达后端服务器。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -6005,6 +6336,14 @@
           <t>GET /../hello.txt返回200 OK, body='HELLO WORLD!!'。绕过Web根目录限制,泄露上级目录文件。该版本路径规范化存在缺陷。</t>
         </is>
       </c>
+      <c r="K44" s="13" t="inlineStr">
+        <is>
+          <t>【敏感文件读取】攻击者可利用lighttpd的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若lighttpd为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="260" customHeight="1">
       <c r="A45" s="6" t="inlineStr">
@@ -6244,6 +6583,14 @@
       <c r="J45" s="6" t="inlineStr">
         <is>
           <t>请求包含嵌入CRLF和完整HTTP响应行,可致响应拆分攻击,注入恶意内容/Set-Cookie。7/10组确认。</t>
+        </is>
+      </c>
+      <c r="K45" s="13" t="inlineStr">
+        <is>
+          <t>【HTTP缓存投毒】攻击者可利用lighttpd的HTTP请求走私/响应分割漏洞，向前端缓存/代理服务器注入恶意HTTP响应，污染缓存内容。后续合法用户请求将收到被篡改的缓存内容，可能导致XSS、恶意重定向或恶意文件下载。
+【会话劫持与凭证窃取】通过HTTP响应头注入，攻击者可构造恶意响应设置Cookie、重定向用户到钓鱼页面，或注入恶意JavaScript代码窃取用户会话令牌和登录凭证。
+【WAF/安全设备绕过】前端代理与后端lighttpd对HTTP请求边界解析不一致，允许恶意请求绕过Web应用防火墙(WAF)的检测规则，直接到达后端服务器。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -6343,6 +6690,14 @@
           <t>GET /../hello.txt返回200 OK, body='HELLO WORLD!!'。绕过Web根目录限制,泄露上级目录文件。该版本路径规范化存在缺陷。</t>
         </is>
       </c>
+      <c r="K46" s="13" t="inlineStr">
+        <is>
+          <t>【敏感文件读取】攻击者可利用lighttpd的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若lighttpd为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="260" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
@@ -6436,6 +6791,14 @@
           <t>多个Content-Length头违反RFC 7230。前后端对请求体边界解析不一致导致HTTP走私攻击。10/10组均发现。</t>
         </is>
       </c>
+      <c r="K47" s="13" t="inlineStr">
+        <is>
+          <t>【HTTP缓存投毒】攻击者可利用lighttpd的HTTP请求走私/响应分割漏洞，向前端缓存/代理服务器注入恶意HTTP响应，污染缓存内容。后续合法用户请求将收到被篡改的缓存内容，可能导致XSS、恶意重定向或恶意文件下载。
+【会话劫持与凭证窃取】通过HTTP响应头注入，攻击者可构造恶意响应设置Cookie、重定向用户到钓鱼页面，或注入恶意JavaScript代码窃取用户会话令牌和登录凭证。
+【WAF/安全设备绕过】前端代理与后端lighttpd对HTTP请求边界解析不一致，允许恶意请求绕过Web应用防火墙(WAF)的检测规则，直接到达后端服务器。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="260" customHeight="1">
       <c r="A48" s="4" t="inlineStr">
@@ -6653,6 +7016,14 @@
       <c r="J48" s="4" t="inlineStr">
         <is>
           <t>多个Content-Length头违反RFC 7230。前后端对请求体边界解析不一致导致HTTP走私攻击。10/10组均发现。</t>
+        </is>
+      </c>
+      <c r="K48" s="13" t="inlineStr">
+        <is>
+          <t>【HTTP缓存投毒】攻击者可利用lighttpd的HTTP请求走私/响应分割漏洞，向前端缓存/代理服务器注入恶意HTTP响应，污染缓存内容。后续合法用户请求将收到被篡改的缓存内容，可能导致XSS、恶意重定向或恶意文件下载。
+【会话劫持与凭证窃取】通过HTTP响应头注入，攻击者可构造恶意响应设置Cookie、重定向用户到钓鱼页面，或注入恶意JavaScript代码窃取用户会话令牌和登录凭证。
+【WAF/安全设备绕过】前端代理与后端lighttpd对HTTP请求边界解析不一致，允许恶意请求绕过Web应用防火墙(WAF)的检测规则，直接到达后端服务器。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -6838,6 +7209,14 @@
       <c r="J49" s="6" t="inlineStr">
         <is>
           <t>请求包含嵌入CRLF和完整HTTP响应行,可致响应拆分攻击,注入恶意内容/Set-Cookie。7/10组确认。</t>
+        </is>
+      </c>
+      <c r="K49" s="13" t="inlineStr">
+        <is>
+          <t>【HTTP缓存投毒】攻击者可利用lighttpd的HTTP请求走私/响应分割漏洞，向前端缓存/代理服务器注入恶意HTTP响应，污染缓存内容。后续合法用户请求将收到被篡改的缓存内容，可能导致XSS、恶意重定向或恶意文件下载。
+【会话劫持与凭证窃取】通过HTTP响应头注入，攻击者可构造恶意响应设置Cookie、重定向用户到钓鱼页面，或注入恶意JavaScript代码窃取用户会话令牌和登录凭证。
+【WAF/安全设备绕过】前端代理与后端lighttpd对HTTP请求边界解析不一致，允许恶意请求绕过Web应用防火墙(WAF)的检测规则，直接到达后端服务器。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -6991,6 +7370,14 @@
       <c r="J50" s="7" t="inlineStr">
         <is>
           <t>通过%00空字节或';'编码技巧绕过URL访问控制。lighttpd历史上存在相同编码绕过漏洞。</t>
+        </is>
+      </c>
+      <c r="K50" s="13" t="inlineStr">
+        <is>
+          <t>【未授权访问】攻击者可绕过lighttpd的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将lighttpd的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除lighttpd管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若lighttpd连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -7284,6 +7671,14 @@
           <t>多个Content-Length头违反RFC 7230。前后端对请求体边界解析不一致导致HTTP走私攻击。10/10组均发现。</t>
         </is>
       </c>
+      <c r="K51" s="13" t="inlineStr">
+        <is>
+          <t>【HTTP缓存投毒】攻击者可利用lighttpd的HTTP请求走私/响应分割漏洞，向前端缓存/代理服务器注入恶意HTTP响应，污染缓存内容。后续合法用户请求将收到被篡改的缓存内容，可能导致XSS、恶意重定向或恶意文件下载。
+【会话劫持与凭证窃取】通过HTTP响应头注入，攻击者可构造恶意响应设置Cookie、重定向用户到钓鱼页面，或注入恶意JavaScript代码窃取用户会话令牌和登录凭证。
+【WAF/安全设备绕过】前端代理与后端lighttpd对HTTP请求边界解析不一致，允许恶意请求绕过Web应用防火墙(WAF)的检测规则，直接到达后端服务器。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="260" customHeight="1">
       <c r="A52" s="4" t="inlineStr">
@@ -7458,6 +7853,14 @@
           <t>多个Content-Length头违反RFC 7230。前后端对请求体边界解析不一致导致HTTP走私攻击。10/10组均发现。</t>
         </is>
       </c>
+      <c r="K52" s="13" t="inlineStr">
+        <is>
+          <t>【HTTP缓存投毒】攻击者可利用lighttpd的HTTP请求走私/响应分割漏洞，向前端缓存/代理服务器注入恶意HTTP响应，污染缓存内容。后续合法用户请求将收到被篡改的缓存内容，可能导致XSS、恶意重定向或恶意文件下载。
+【会话劫持与凭证窃取】通过HTTP响应头注入，攻击者可构造恶意响应设置Cookie、重定向用户到钓鱼页面，或注入恶意JavaScript代码窃取用户会话令牌和登录凭证。
+【WAF/安全设备绕过】前端代理与后端lighttpd对HTTP请求边界解析不一致，允许恶意请求绕过Web应用防火墙(WAF)的检测规则，直接到达后端服务器。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="260" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
@@ -7725,6 +8128,14 @@
       <c r="J53" s="4" t="inlineStr">
         <is>
           <t>多个Content-Length头违反RFC 7230。前后端对请求体边界解析不一致导致HTTP走私攻击。10/10组均发现。</t>
+        </is>
+      </c>
+      <c r="K53" s="13" t="inlineStr">
+        <is>
+          <t>【HTTP缓存投毒】攻击者可利用lighttpd的HTTP请求走私/响应分割漏洞，向前端缓存/代理服务器注入恶意HTTP响应，污染缓存内容。后续合法用户请求将收到被篡改的缓存内容，可能导致XSS、恶意重定向或恶意文件下载。
+【会话劫持与凭证窃取】通过HTTP响应头注入，攻击者可构造恶意响应设置Cookie、重定向用户到钓鱼页面，或注入恶意JavaScript代码窃取用户会话令牌和登录凭证。
+【WAF/安全设备绕过】前端代理与后端lighttpd对HTTP请求边界解析不一致，允许恶意请求绕过Web应用防火墙(WAF)的检测规则，直接到达后端服务器。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -7837,6 +8248,14 @@
           <t>通过%00空字节或';'编码技巧绕过URL访问控制。lighttpd历史上存在相同编码绕过漏洞。</t>
         </is>
       </c>
+      <c r="K54" s="13" t="inlineStr">
+        <is>
+          <t>【未授权访问】攻击者可绕过lighttpd的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将lighttpd的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除lighttpd管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若lighttpd连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="260" customHeight="1">
       <c r="A55" s="4" t="inlineStr">
@@ -7965,6 +8384,14 @@
       <c r="J55" s="4" t="inlineStr">
         <is>
           <t>多个Content-Length头违反RFC 7230。前后端对请求体边界解析不一致导致HTTP走私攻击。10/10组均发现。</t>
+        </is>
+      </c>
+      <c r="K55" s="13" t="inlineStr">
+        <is>
+          <t>【HTTP缓存投毒】攻击者可利用lighttpd的HTTP请求走私/响应分割漏洞，向前端缓存/代理服务器注入恶意HTTP响应，污染缓存内容。后续合法用户请求将收到被篡改的缓存内容，可能导致XSS、恶意重定向或恶意文件下载。
+【会话劫持与凭证窃取】通过HTTP响应头注入，攻击者可构造恶意响应设置Cookie、重定向用户到钓鱼页面，或注入恶意JavaScript代码窃取用户会话令牌和登录凭证。
+【WAF/安全设备绕过】前端代理与后端lighttpd对HTTP请求边界解析不一致，允许恶意请求绕过Web应用防火墙(WAF)的检测规则，直接到达后端服务器。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -8153,6 +8580,14 @@
           <t>多个Content-Length头违反RFC 7230。前后端对请求体边界解析不一致导致HTTP走私攻击。10/10组均发现。</t>
         </is>
       </c>
+      <c r="K56" s="13" t="inlineStr">
+        <is>
+          <t>【HTTP缓存投毒】攻击者可利用lighttpd的HTTP请求走私/响应分割漏洞，向前端缓存/代理服务器注入恶意HTTP响应，污染缓存内容。后续合法用户请求将收到被篡改的缓存内容，可能导致XSS、恶意重定向或恶意文件下载。
+【会话劫持与凭证窃取】通过HTTP响应头注入，攻击者可构造恶意响应设置Cookie、重定向用户到钓鱼页面，或注入恶意JavaScript代码窃取用户会话令牌和登录凭证。
+【WAF/安全设备绕过】前端代理与后端lighttpd对HTTP请求边界解析不一致，允许恶意请求绕过Web应用防火墙(WAF)的检测规则，直接到达后端服务器。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="260" customHeight="1">
       <c r="A57" s="5" t="inlineStr">
@@ -8265,6 +8700,14 @@
       <c r="J57" s="5" t="inlineStr">
         <is>
           <t>GET /../hello.txt返回200 OK, body='HELLO WORLD!!'。绕过Web根目录限制,泄露上级目录文件。该版本路径规范化存在缺陷。</t>
+        </is>
+      </c>
+      <c r="K57" s="13" t="inlineStr">
+        <is>
+          <t>【敏感文件读取】攻击者可利用lighttpd的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若lighttpd为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -8530,6 +8973,14 @@
           <t>多个Content-Length头违反RFC 7230。前后端对请求体边界解析不一致导致HTTP走私攻击。10/10组均发现。</t>
         </is>
       </c>
+      <c r="K58" s="13" t="inlineStr">
+        <is>
+          <t>【HTTP缓存投毒】攻击者可利用lighttpd的HTTP请求走私/响应分割漏洞，向前端缓存/代理服务器注入恶意HTTP响应，污染缓存内容。后续合法用户请求将收到被篡改的缓存内容，可能导致XSS、恶意重定向或恶意文件下载。
+【会话劫持与凭证窃取】通过HTTP响应头注入，攻击者可构造恶意响应设置Cookie、重定向用户到钓鱼页面，或注入恶意JavaScript代码窃取用户会话令牌和登录凭证。
+【WAF/安全设备绕过】前端代理与后端lighttpd对HTTP请求边界解析不一致，允许恶意请求绕过Web应用防火墙(WAF)的检测规则，直接到达后端服务器。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="260" customHeight="1">
       <c r="A59" s="5" t="inlineStr">
@@ -8638,6 +9089,14 @@
           <t>GET /../hello.txt返回200 OK, body='HELLO WORLD!!'。绕过Web根目录限制,泄露上级目录文件。该版本路径规范化存在缺陷。</t>
         </is>
       </c>
+      <c r="K59" s="13" t="inlineStr">
+        <is>
+          <t>【敏感文件读取】攻击者可利用lighttpd的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若lighttpd为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="260" customHeight="1">
       <c r="A60" s="5" t="inlineStr">
@@ -8730,6 +9189,14 @@
       <c r="J60" s="5" t="inlineStr">
         <is>
           <t>GET /../hello.txt返回200 OK, body='HELLO WORLD!!'。绕过Web根目录限制,泄露上级目录文件。该版本路径规范化存在缺陷。</t>
+        </is>
+      </c>
+      <c r="K60" s="13" t="inlineStr">
+        <is>
+          <t>【敏感文件读取】攻击者可利用lighttpd的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若lighttpd为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -8995,6 +9462,14 @@
       <c r="J61" s="4" t="inlineStr">
         <is>
           <t>多个Content-Length头违反RFC 7230。前后端对请求体边界解析不一致导致HTTP走私攻击。10/10组均发现。</t>
+        </is>
+      </c>
+      <c r="K61" s="13" t="inlineStr">
+        <is>
+          <t>【HTTP缓存投毒】攻击者可利用lighttpd的HTTP请求走私/响应分割漏洞，向前端缓存/代理服务器注入恶意HTTP响应，污染缓存内容。后续合法用户请求将收到被篡改的缓存内容，可能导致XSS、恶意重定向或恶意文件下载。
+【会话劫持与凭证窃取】通过HTTP响应头注入，攻击者可构造恶意响应设置Cookie、重定向用户到钓鱼页面，或注入恶意JavaScript代码窃取用户会话令牌和登录凭证。
+【WAF/安全设备绕过】前端代理与后端lighttpd对HTTP请求边界解析不一致，允许恶意请求绕过Web应用防火墙(WAF)的检测规则，直接到达后端服务器。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -9262,6 +9737,14 @@
           <t>GET /../hello.txt返回200 OK, body='HELLO WORLD!!'。绕过Web根目录限制,泄露上级目录文件。该版本路径规范化存在缺陷。</t>
         </is>
       </c>
+      <c r="K62" s="13" t="inlineStr">
+        <is>
+          <t>【敏感文件读取】攻击者可利用lighttpd的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若lighttpd为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="260" customHeight="1">
       <c r="A63" s="5" t="inlineStr">
@@ -9357,6 +9840,14 @@
       <c r="J63" s="5" t="inlineStr">
         <is>
           <t>GET /../hello.txt返回200 OK, body='HELLO WORLD!!'。绕过Web根目录限制,泄露上级目录文件。该版本路径规范化存在缺陷。</t>
+        </is>
+      </c>
+      <c r="K63" s="13" t="inlineStr">
+        <is>
+          <t>【敏感文件读取】攻击者可利用lighttpd的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若lighttpd为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -9468,6 +9959,14 @@
           <t>多个Content-Length头违反RFC 7230。前后端对请求体边界解析不一致导致HTTP走私攻击。10/10组均发现。</t>
         </is>
       </c>
+      <c r="K64" s="13" t="inlineStr">
+        <is>
+          <t>【HTTP缓存投毒】攻击者可利用lighttpd的HTTP请求走私/响应分割漏洞，向前端缓存/代理服务器注入恶意HTTP响应，污染缓存内容。后续合法用户请求将收到被篡改的缓存内容，可能导致XSS、恶意重定向或恶意文件下载。
+【会话劫持与凭证窃取】通过HTTP响应头注入，攻击者可构造恶意响应设置Cookie、重定向用户到钓鱼页面，或注入恶意JavaScript代码窃取用户会话令牌和登录凭证。
+【WAF/安全设备绕过】前端代理与后端lighttpd对HTTP请求边界解析不一致，允许恶意请求绕过Web应用防火墙(WAF)的检测规则，直接到达后端服务器。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="260" customHeight="1">
       <c r="A65" s="6" t="inlineStr">
@@ -9633,6 +10132,14 @@
       <c r="J65" s="6" t="inlineStr">
         <is>
           <t>请求包含嵌入CRLF和完整HTTP响应行,可致响应拆分攻击,注入恶意内容/Set-Cookie。7/10组确认。</t>
+        </is>
+      </c>
+      <c r="K65" s="13" t="inlineStr">
+        <is>
+          <t>【HTTP缓存投毒】攻击者可利用lighttpd的HTTP请求走私/响应分割漏洞，向前端缓存/代理服务器注入恶意HTTP响应，污染缓存内容。后续合法用户请求将收到被篡改的缓存内容，可能导致XSS、恶意重定向或恶意文件下载。
+【会话劫持与凭证窃取】通过HTTP响应头注入，攻击者可构造恶意响应设置Cookie、重定向用户到钓鱼页面，或注入恶意JavaScript代码窃取用户会话令牌和登录凭证。
+【WAF/安全设备绕过】前端代理与后端lighttpd对HTTP请求边界解析不一致，允许恶意请求绕过Web应用防火墙(WAF)的检测规则，直接到达后端服务器。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -9743,6 +10250,14 @@
       <c r="J66" s="5" t="inlineStr">
         <is>
           <t>GET /../hello.txt返回200 OK, body='HELLO WORLD!!'。绕过Web根目录限制,泄露上级目录文件。该版本路径规范化存在缺陷。</t>
+        </is>
+      </c>
+      <c r="K66" s="13" t="inlineStr">
+        <is>
+          <t>【敏感文件读取】攻击者可利用lighttpd的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若lighttpd为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -9913,6 +10428,14 @@
           <t>多个Content-Length头违反RFC 7230。前后端对请求体边界解析不一致导致HTTP走私攻击。10/10组均发现。</t>
         </is>
       </c>
+      <c r="K67" s="13" t="inlineStr">
+        <is>
+          <t>【HTTP缓存投毒】攻击者可利用lighttpd的HTTP请求走私/响应分割漏洞，向前端缓存/代理服务器注入恶意HTTP响应，污染缓存内容。后续合法用户请求将收到被篡改的缓存内容，可能导致XSS、恶意重定向或恶意文件下载。
+【会话劫持与凭证窃取】通过HTTP响应头注入，攻击者可构造恶意响应设置Cookie、重定向用户到钓鱼页面，或注入恶意JavaScript代码窃取用户会话令牌和登录凭证。
+【WAF/安全设备绕过】前端代理与后端lighttpd对HTTP请求边界解析不一致，允许恶意请求绕过Web应用防火墙(WAF)的检测规则，直接到达后端服务器。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="260" customHeight="1">
       <c r="A68" s="4" t="inlineStr">
@@ -10010,6 +10533,14 @@
           <t>多个Content-Length头违反RFC 7230。前后端对请求体边界解析不一致导致HTTP走私攻击。10/10组均发现。</t>
         </is>
       </c>
+      <c r="K68" s="13" t="inlineStr">
+        <is>
+          <t>【HTTP缓存投毒】攻击者可利用lighttpd的HTTP请求走私/响应分割漏洞，向前端缓存/代理服务器注入恶意HTTP响应，污染缓存内容。后续合法用户请求将收到被篡改的缓存内容，可能导致XSS、恶意重定向或恶意文件下载。
+【会话劫持与凭证窃取】通过HTTP响应头注入，攻击者可构造恶意响应设置Cookie、重定向用户到钓鱼页面，或注入恶意JavaScript代码窃取用户会话令牌和登录凭证。
+【WAF/安全设备绕过】前端代理与后端lighttpd对HTTP请求边界解析不一致，允许恶意请求绕过Web应用防火墙(WAF)的检测规则，直接到达后端服务器。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="260" customHeight="1">
       <c r="A69" s="5" t="inlineStr">
@@ -10110,6 +10641,14 @@
           <t>GET /../hello.txt返回200 OK, body='HELLO WORLD!!'。绕过Web根目录限制,泄露上级目录文件。该版本路径规范化存在缺陷。</t>
         </is>
       </c>
+      <c r="K69" s="13" t="inlineStr">
+        <is>
+          <t>【敏感文件读取】攻击者可利用lighttpd的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若lighttpd为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="260" customHeight="1">
       <c r="A70" s="6" t="inlineStr">
@@ -10242,6 +10781,14 @@
       <c r="J70" s="6" t="inlineStr">
         <is>
           <t>请求包含嵌入CRLF和完整HTTP响应行,可致响应拆分攻击,注入恶意内容/Set-Cookie。7/10组确认。</t>
+        </is>
+      </c>
+      <c r="K70" s="13" t="inlineStr">
+        <is>
+          <t>【HTTP缓存投毒】攻击者可利用lighttpd的HTTP请求走私/响应分割漏洞，向前端缓存/代理服务器注入恶意HTTP响应，污染缓存内容。后续合法用户请求将收到被篡改的缓存内容，可能导致XSS、恶意重定向或恶意文件下载。
+【会话劫持与凭证窃取】通过HTTP响应头注入，攻击者可构造恶意响应设置Cookie、重定向用户到钓鱼页面，或注入恶意JavaScript代码窃取用户会话令牌和登录凭证。
+【WAF/安全设备绕过】前端代理与后端lighttpd对HTTP请求边界解析不一致，允许恶意请求绕过Web应用防火墙(WAF)的检测规则，直接到达后端服务器。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -10366,6 +10913,14 @@
           <t>GET /../hello.txt返回200 OK, body='HELLO WORLD!!'。绕过Web根目录限制,泄露上级目录文件。该版本路径规范化存在缺陷。</t>
         </is>
       </c>
+      <c r="K71" s="13" t="inlineStr">
+        <is>
+          <t>【敏感文件读取】攻击者可利用lighttpd的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若lighttpd为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="260" customHeight="1">
       <c r="A72" s="4" t="inlineStr">
@@ -10458,6 +11013,14 @@
           <t>多个Content-Length头违反RFC 7230。前后端对请求体边界解析不一致导致HTTP走私攻击。10/10组均发现。</t>
         </is>
       </c>
+      <c r="K72" s="13" t="inlineStr">
+        <is>
+          <t>【HTTP缓存投毒】攻击者可利用lighttpd的HTTP请求走私/响应分割漏洞，向前端缓存/代理服务器注入恶意HTTP响应，污染缓存内容。后续合法用户请求将收到被篡改的缓存内容，可能导致XSS、恶意重定向或恶意文件下载。
+【会话劫持与凭证窃取】通过HTTP响应头注入，攻击者可构造恶意响应设置Cookie、重定向用户到钓鱼页面，或注入恶意JavaScript代码窃取用户会话令牌和登录凭证。
+【WAF/安全设备绕过】前端代理与后端lighttpd对HTTP请求边界解析不一致，允许恶意请求绕过Web应用防火墙(WAF)的检测规则，直接到达后端服务器。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="260" customHeight="1">
       <c r="A73" s="4" t="inlineStr">
@@ -10555,6 +11118,14 @@
           <t>多个Content-Length头违反RFC 7230。前后端对请求体边界解析不一致导致HTTP走私攻击。10/10组均发现。</t>
         </is>
       </c>
+      <c r="K73" s="13" t="inlineStr">
+        <is>
+          <t>【HTTP缓存投毒】攻击者可利用lighttpd的HTTP请求走私/响应分割漏洞，向前端缓存/代理服务器注入恶意HTTP响应，污染缓存内容。后续合法用户请求将收到被篡改的缓存内容，可能导致XSS、恶意重定向或恶意文件下载。
+【会话劫持与凭证窃取】通过HTTP响应头注入，攻击者可构造恶意响应设置Cookie、重定向用户到钓鱼页面，或注入恶意JavaScript代码窃取用户会话令牌和登录凭证。
+【WAF/安全设备绕过】前端代理与后端lighttpd对HTTP请求边界解析不一致，允许恶意请求绕过Web应用防火墙(WAF)的检测规则，直接到达后端服务器。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="260" customHeight="1">
       <c r="A74" s="5" t="inlineStr">
@@ -10655,6 +11226,14 @@
           <t>GET /../hello.txt返回200 OK, body='HELLO WORLD!!'。绕过Web根目录限制,泄露上级目录文件。该版本路径规范化存在缺陷。</t>
         </is>
       </c>
+      <c r="K74" s="13" t="inlineStr">
+        <is>
+          <t>【敏感文件读取】攻击者可利用lighttpd的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若lighttpd为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="260" customHeight="1">
       <c r="A75" s="4" t="inlineStr">
@@ -10779,6 +11358,14 @@
       <c r="J75" s="4" t="inlineStr">
         <is>
           <t>多个Content-Length头违反RFC 7230。前后端对请求体边界解析不一致导致HTTP走私攻击。10/10组均发现。</t>
+        </is>
+      </c>
+      <c r="K75" s="13" t="inlineStr">
+        <is>
+          <t>【HTTP缓存投毒】攻击者可利用lighttpd的HTTP请求走私/响应分割漏洞，向前端缓存/代理服务器注入恶意HTTP响应，污染缓存内容。后续合法用户请求将收到被篡改的缓存内容，可能导致XSS、恶意重定向或恶意文件下载。
+【会话劫持与凭证窃取】通过HTTP响应头注入，攻击者可构造恶意响应设置Cookie、重定向用户到钓鱼页面，或注入恶意JavaScript代码窃取用户会话令牌和登录凭证。
+【WAF/安全设备绕过】前端代理与后端lighttpd对HTTP请求边界解析不一致，允许恶意请求绕过Web应用防火墙(WAF)的检测规则，直接到达后端服务器。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -10876,6 +11463,14 @@
       <c r="J76" s="5" t="inlineStr">
         <is>
           <t>GET /../hello.txt返回200 OK, body='HELLO WORLD!!'。绕过Web根目录限制,泄露上级目录文件。该版本路径规范化存在缺陷。</t>
+        </is>
+      </c>
+      <c r="K76" s="13" t="inlineStr">
+        <is>
+          <t>【敏感文件读取】攻击者可利用lighttpd的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若lighttpd为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -11130,6 +11725,14 @@
           <t>多个Content-Length头违反RFC 7230。前后端对请求体边界解析不一致导致HTTP走私攻击。10/10组均发现。</t>
         </is>
       </c>
+      <c r="K77" s="13" t="inlineStr">
+        <is>
+          <t>【HTTP缓存投毒】攻击者可利用lighttpd的HTTP请求走私/响应分割漏洞，向前端缓存/代理服务器注入恶意HTTP响应，污染缓存内容。后续合法用户请求将收到被篡改的缓存内容，可能导致XSS、恶意重定向或恶意文件下载。
+【会话劫持与凭证窃取】通过HTTP响应头注入，攻击者可构造恶意响应设置Cookie、重定向用户到钓鱼页面，或注入恶意JavaScript代码窃取用户会话令牌和登录凭证。
+【WAF/安全设备绕过】前端代理与后端lighttpd对HTTP请求边界解析不一致，允许恶意请求绕过Web应用防火墙(WAF)的检测规则，直接到达后端服务器。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="260" customHeight="1">
       <c r="A78" s="4" t="inlineStr">
@@ -11290,6 +11893,14 @@
       <c r="J78" s="4" t="inlineStr">
         <is>
           <t>多个Content-Length头违反RFC 7230。前后端对请求体边界解析不一致导致HTTP走私攻击。10/10组均发现。</t>
+        </is>
+      </c>
+      <c r="K78" s="13" t="inlineStr">
+        <is>
+          <t>【HTTP缓存投毒】攻击者可利用lighttpd的HTTP请求走私/响应分割漏洞，向前端缓存/代理服务器注入恶意HTTP响应，污染缓存内容。后续合法用户请求将收到被篡改的缓存内容，可能导致XSS、恶意重定向或恶意文件下载。
+【会话劫持与凭证窃取】通过HTTP响应头注入，攻击者可构造恶意响应设置Cookie、重定向用户到钓鱼页面，或注入恶意JavaScript代码窃取用户会话令牌和登录凭证。
+【WAF/安全设备绕过】前端代理与后端lighttpd对HTTP请求边界解析不一致，允许恶意请求绕过Web应用防火墙(WAF)的检测规则，直接到达后端服务器。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -11594,6 +12205,14 @@
           <t>GET /../hello.txt返回200 OK, body='HELLO WORLD!!'。绕过Web根目录限制,泄露上级目录文件。该版本路径规范化存在缺陷。</t>
         </is>
       </c>
+      <c r="K79" s="13" t="inlineStr">
+        <is>
+          <t>【敏感文件读取】攻击者可利用lighttpd的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若lighttpd为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="260" customHeight="1">
       <c r="A80" s="4" t="inlineStr">
@@ -11809,6 +12428,14 @@
           <t>多个Content-Length头违反RFC 7230。前后端对请求体边界解析不一致导致HTTP走私攻击。10/10组均发现。</t>
         </is>
       </c>
+      <c r="K80" s="13" t="inlineStr">
+        <is>
+          <t>【HTTP缓存投毒】攻击者可利用lighttpd的HTTP请求走私/响应分割漏洞，向前端缓存/代理服务器注入恶意HTTP响应，污染缓存内容。后续合法用户请求将收到被篡改的缓存内容，可能导致XSS、恶意重定向或恶意文件下载。
+【会话劫持与凭证窃取】通过HTTP响应头注入，攻击者可构造恶意响应设置Cookie、重定向用户到钓鱼页面，或注入恶意JavaScript代码窃取用户会话令牌和登录凭证。
+【WAF/安全设备绕过】前端代理与后端lighttpd对HTTP请求边界解析不一致，允许恶意请求绕过Web应用防火墙(WAF)的检测规则，直接到达后端服务器。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="260" customHeight="1">
       <c r="A81" s="5" t="inlineStr">
@@ -11960,6 +12587,14 @@
       <c r="J81" s="5" t="inlineStr">
         <is>
           <t>GET /../hello.txt返回200 OK, body='HELLO WORLD!!'。绕过Web根目录限制,泄露上级目录文件。该版本路径规范化存在缺陷。</t>
+        </is>
+      </c>
+      <c r="K81" s="13" t="inlineStr">
+        <is>
+          <t>【敏感文件读取】攻击者可利用lighttpd的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若lighttpd为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -12104,6 +12739,14 @@
           <t>Content-Length与Transfer-Encoding同时存在,违反RFC 7230。前后端解析差异可致HTTP走私/缓存投毒/请求劫持。</t>
         </is>
       </c>
+      <c r="K82" s="13" t="inlineStr">
+        <is>
+          <t>【HTTP缓存投毒】攻击者可利用lighttpd的HTTP请求走私/响应分割漏洞，向前端缓存/代理服务器注入恶意HTTP响应，污染缓存内容。后续合法用户请求将收到被篡改的缓存内容，可能导致XSS、恶意重定向或恶意文件下载。
+【会话劫持与凭证窃取】通过HTTP响应头注入，攻击者可构造恶意响应设置Cookie、重定向用户到钓鱼页面，或注入恶意JavaScript代码窃取用户会话令牌和登录凭证。
+【WAF/安全设备绕过】前端代理与后端lighttpd对HTTP请求边界解析不一致，允许恶意请求绕过Web应用防火墙(WAF)的检测规则，直接到达后端服务器。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="260" customHeight="1">
       <c r="A83" s="4" t="inlineStr">
@@ -12202,6 +12845,14 @@
       <c r="J83" s="4" t="inlineStr">
         <is>
           <t>多个Content-Length头违反RFC 7230。前后端对请求体边界解析不一致导致HTTP走私攻击。10/10组均发现。</t>
+        </is>
+      </c>
+      <c r="K83" s="13" t="inlineStr">
+        <is>
+          <t>【HTTP缓存投毒】攻击者可利用lighttpd的HTTP请求走私/响应分割漏洞，向前端缓存/代理服务器注入恶意HTTP响应，污染缓存内容。后续合法用户请求将收到被篡改的缓存内容，可能导致XSS、恶意重定向或恶意文件下载。
+【会话劫持与凭证窃取】通过HTTP响应头注入，攻击者可构造恶意响应设置Cookie、重定向用户到钓鱼页面，或注入恶意JavaScript代码窃取用户会话令牌和登录凭证。
+【WAF/安全设备绕过】前端代理与后端lighttpd对HTTP请求边界解析不一致，允许恶意请求绕过Web应用防火墙(WAF)的检测规则，直接到达后端服务器。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -12452,6 +13103,14 @@
           <t>GET /../hello.txt返回200 OK, body='HELLO WORLD!!'。绕过Web根目录限制,泄露上级目录文件。该版本路径规范化存在缺陷。</t>
         </is>
       </c>
+      <c r="K84" s="13" t="inlineStr">
+        <is>
+          <t>【敏感文件读取】攻击者可利用lighttpd的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若lighttpd为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="260" customHeight="1">
       <c r="A85" s="6" t="inlineStr">
@@ -12542,6 +13201,14 @@
       <c r="J85" s="6" t="inlineStr">
         <is>
           <t>请求包含嵌入CRLF和完整HTTP响应行,可致响应拆分攻击,注入恶意内容/Set-Cookie。7/10组确认。</t>
+        </is>
+      </c>
+      <c r="K85" s="13" t="inlineStr">
+        <is>
+          <t>【HTTP缓存投毒】攻击者可利用lighttpd的HTTP请求走私/响应分割漏洞，向前端缓存/代理服务器注入恶意HTTP响应，污染缓存内容。后续合法用户请求将收到被篡改的缓存内容，可能导致XSS、恶意重定向或恶意文件下载。
+【会话劫持与凭证窃取】通过HTTP响应头注入，攻击者可构造恶意响应设置Cookie、重定向用户到钓鱼页面，或注入恶意JavaScript代码窃取用户会话令牌和登录凭证。
+【WAF/安全设备绕过】前端代理与后端lighttpd对HTTP请求边界解析不一致，允许恶意请求绕过Web应用防火墙(WAF)的检测规则，直接到达后端服务器。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -12760,6 +13427,14 @@
           <t>Content-Length与Transfer-Encoding同时存在,违反RFC 7230。前后端解析差异可致HTTP走私/缓存投毒/请求劫持。</t>
         </is>
       </c>
+      <c r="K86" s="13" t="inlineStr">
+        <is>
+          <t>【HTTP缓存投毒】攻击者可利用lighttpd的HTTP请求走私/响应分割漏洞，向前端缓存/代理服务器注入恶意HTTP响应，污染缓存内容。后续合法用户请求将收到被篡改的缓存内容，可能导致XSS、恶意重定向或恶意文件下载。
+【会话劫持与凭证窃取】通过HTTP响应头注入，攻击者可构造恶意响应设置Cookie、重定向用户到钓鱼页面，或注入恶意JavaScript代码窃取用户会话令牌和登录凭证。
+【WAF/安全设备绕过】前端代理与后端lighttpd对HTTP请求边界解析不一致，允许恶意请求绕过Web应用防火墙(WAF)的检测规则，直接到达后端服务器。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="260" customHeight="1">
       <c r="A87" s="5" t="inlineStr">
@@ -12859,6 +13534,14 @@
           <t>GET /../hello.txt返回200 OK, body='HELLO WORLD!!'。绕过Web根目录限制,泄露上级目录文件。该版本路径规范化存在缺陷。</t>
         </is>
       </c>
+      <c r="K87" s="13" t="inlineStr">
+        <is>
+          <t>【敏感文件读取】攻击者可利用lighttpd的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若lighttpd为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="260" customHeight="1">
       <c r="A88" s="5" t="inlineStr">
@@ -12984,6 +13667,14 @@
           <t>GET /../hello.txt返回200 OK, body='HELLO WORLD!!'。绕过Web根目录限制,泄露上级目录文件。该版本路径规范化存在缺陷。</t>
         </is>
       </c>
+      <c r="K88" s="13" t="inlineStr">
+        <is>
+          <t>【敏感文件读取】攻击者可利用lighttpd的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若lighttpd为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="260" customHeight="1">
       <c r="A89" s="4" t="inlineStr">
@@ -13076,6 +13767,14 @@
           <t>多个Content-Length头违反RFC 7230。前后端对请求体边界解析不一致导致HTTP走私攻击。10/10组均发现。</t>
         </is>
       </c>
+      <c r="K89" s="13" t="inlineStr">
+        <is>
+          <t>【HTTP缓存投毒】攻击者可利用lighttpd的HTTP请求走私/响应分割漏洞，向前端缓存/代理服务器注入恶意HTTP响应，污染缓存内容。后续合法用户请求将收到被篡改的缓存内容，可能导致XSS、恶意重定向或恶意文件下载。
+【会话劫持与凭证窃取】通过HTTP响应头注入，攻击者可构造恶意响应设置Cookie、重定向用户到钓鱼页面，或注入恶意JavaScript代码窃取用户会话令牌和登录凭证。
+【WAF/安全设备绕过】前端代理与后端lighttpd对HTTP请求边界解析不一致，允许恶意请求绕过Web应用防火墙(WAF)的检测规则，直接到达后端服务器。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="260" customHeight="1">
       <c r="A90" s="5" t="inlineStr">
@@ -13183,6 +13882,14 @@
       <c r="J90" s="5" t="inlineStr">
         <is>
           <t>GET /../hello.txt返回200 OK, body='HELLO WORLD!!'。绕过Web根目录限制,泄露上级目录文件。该版本路径规范化存在缺陷。</t>
+        </is>
+      </c>
+      <c r="K90" s="13" t="inlineStr">
+        <is>
+          <t>【敏感文件读取】攻击者可利用lighttpd的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若lighttpd为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -13314,6 +14021,14 @@
           <t>多个Content-Length头违反RFC 7230。前后端对请求体边界解析不一致导致HTTP走私攻击。10/10组均发现。</t>
         </is>
       </c>
+      <c r="K91" s="13" t="inlineStr">
+        <is>
+          <t>【HTTP缓存投毒】攻击者可利用lighttpd的HTTP请求走私/响应分割漏洞，向前端缓存/代理服务器注入恶意HTTP响应，污染缓存内容。后续合法用户请求将收到被篡改的缓存内容，可能导致XSS、恶意重定向或恶意文件下载。
+【会话劫持与凭证窃取】通过HTTP响应头注入，攻击者可构造恶意响应设置Cookie、重定向用户到钓鱼页面，或注入恶意JavaScript代码窃取用户会话令牌和登录凭证。
+【WAF/安全设备绕过】前端代理与后端lighttpd对HTTP请求边界解析不一致，允许恶意请求绕过Web应用防火墙(WAF)的检测规则，直接到达后端服务器。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="260" customHeight="1">
       <c r="A92" s="4" t="inlineStr">
@@ -13400,6 +14115,14 @@
       <c r="J92" s="4" t="inlineStr">
         <is>
           <t>多个Content-Length头违反RFC 7230。前后端对请求体边界解析不一致导致HTTP走私攻击。10/10组均发现。</t>
+        </is>
+      </c>
+      <c r="K92" s="13" t="inlineStr">
+        <is>
+          <t>【HTTP缓存投毒】攻击者可利用lighttpd的HTTP请求走私/响应分割漏洞，向前端缓存/代理服务器注入恶意HTTP响应，污染缓存内容。后续合法用户请求将收到被篡改的缓存内容，可能导致XSS、恶意重定向或恶意文件下载。
+【会话劫持与凭证窃取】通过HTTP响应头注入，攻击者可构造恶意响应设置Cookie、重定向用户到钓鱼页面，或注入恶意JavaScript代码窃取用户会话令牌和登录凭证。
+【WAF/安全设备绕过】前端代理与后端lighttpd对HTTP请求边界解析不一致，允许恶意请求绕过Web应用防火墙(WAF)的检测规则，直接到达后端服务器。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -13519,6 +14242,14 @@
           <t>GET /../hello.txt返回200 OK, body='HELLO WORLD!!'。绕过Web根目录限制,泄露上级目录文件。该版本路径规范化存在缺陷。</t>
         </is>
       </c>
+      <c r="K93" s="13" t="inlineStr">
+        <is>
+          <t>【敏感文件读取】攻击者可利用lighttpd的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若lighttpd为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="260" customHeight="1">
       <c r="A94" s="5" t="inlineStr">
@@ -13611,6 +14342,14 @@
           <t>GET /../hello.txt返回200 OK, body='HELLO WORLD!!'。绕过Web根目录限制,泄露上级目录文件。该版本路径规范化存在缺陷。</t>
         </is>
       </c>
+      <c r="K94" s="13" t="inlineStr">
+        <is>
+          <t>【敏感文件读取】攻击者可利用lighttpd的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若lighttpd为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="260" customHeight="1">
       <c r="A95" s="4" t="inlineStr">
@@ -13780,6 +14519,14 @@
           <t>多个Content-Length头违反RFC 7230。前后端对请求体边界解析不一致导致HTTP走私攻击。10/10组均发现。</t>
         </is>
       </c>
+      <c r="K95" s="13" t="inlineStr">
+        <is>
+          <t>【HTTP缓存投毒】攻击者可利用lighttpd的HTTP请求走私/响应分割漏洞，向前端缓存/代理服务器注入恶意HTTP响应，污染缓存内容。后续合法用户请求将收到被篡改的缓存内容，可能导致XSS、恶意重定向或恶意文件下载。
+【会话劫持与凭证窃取】通过HTTP响应头注入，攻击者可构造恶意响应设置Cookie、重定向用户到钓鱼页面，或注入恶意JavaScript代码窃取用户会话令牌和登录凭证。
+【WAF/安全设备绕过】前端代理与后端lighttpd对HTTP请求边界解析不一致，允许恶意请求绕过Web应用防火墙(WAF)的检测规则，直接到达后端服务器。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="260" customHeight="1">
       <c r="A96" s="5" t="inlineStr">
@@ -13938,6 +14685,14 @@
           <t>GET /../hello.txt返回200 OK, body='HELLO WORLD!!'。绕过Web根目录限制,泄露上级目录文件。该版本路径规范化存在缺陷。</t>
         </is>
       </c>
+      <c r="K96" s="13" t="inlineStr">
+        <is>
+          <t>【敏感文件读取】攻击者可利用lighttpd的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若lighttpd为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="260" customHeight="1">
       <c r="A97" s="7" t="inlineStr">
@@ -14044,6 +14799,14 @@
           <t>通过%00空字节或';'编码技巧绕过URL访问控制。lighttpd历史上存在相同编码绕过漏洞。</t>
         </is>
       </c>
+      <c r="K97" s="13" t="inlineStr">
+        <is>
+          <t>【未授权访问】攻击者可绕过lighttpd的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将lighttpd的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除lighttpd管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若lighttpd连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="260" customHeight="1">
       <c r="A98" s="5" t="inlineStr">
@@ -14160,6 +14923,14 @@
       <c r="J98" s="5" t="inlineStr">
         <is>
           <t>GET /../hello.txt返回200 OK, body='HELLO WORLD!!'。绕过Web根目录限制,泄露上级目录文件。该版本路径规范化存在缺陷。</t>
+        </is>
+      </c>
+      <c r="K98" s="13" t="inlineStr">
+        <is>
+          <t>【敏感文件读取】攻击者可利用lighttpd的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若lighttpd为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -14294,6 +15065,14 @@
           <t>多个Content-Length头违反RFC 7230。前后端对请求体边界解析不一致导致HTTP走私攻击。10/10组均发现。</t>
         </is>
       </c>
+      <c r="K99" s="13" t="inlineStr">
+        <is>
+          <t>【HTTP缓存投毒】攻击者可利用lighttpd的HTTP请求走私/响应分割漏洞，向前端缓存/代理服务器注入恶意HTTP响应，污染缓存内容。后续合法用户请求将收到被篡改的缓存内容，可能导致XSS、恶意重定向或恶意文件下载。
+【会话劫持与凭证窃取】通过HTTP响应头注入，攻击者可构造恶意响应设置Cookie、重定向用户到钓鱼页面，或注入恶意JavaScript代码窃取用户会话令牌和登录凭证。
+【WAF/安全设备绕过】前端代理与后端lighttpd对HTTP请求边界解析不一致，允许恶意请求绕过Web应用防火墙(WAF)的检测规则，直接到达后端服务器。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="260" customHeight="1">
       <c r="A100" s="4" t="inlineStr">
@@ -14382,6 +15161,14 @@
       <c r="J100" s="4" t="inlineStr">
         <is>
           <t>多个Content-Length头违反RFC 7230。前后端对请求体边界解析不一致导致HTTP走私攻击。10/10组均发现。</t>
+        </is>
+      </c>
+      <c r="K100" s="13" t="inlineStr">
+        <is>
+          <t>【HTTP缓存投毒】攻击者可利用lighttpd的HTTP请求走私/响应分割漏洞，向前端缓存/代理服务器注入恶意HTTP响应，污染缓存内容。后续合法用户请求将收到被篡改的缓存内容，可能导致XSS、恶意重定向或恶意文件下载。
+【会话劫持与凭证窃取】通过HTTP响应头注入，攻击者可构造恶意响应设置Cookie、重定向用户到钓鱼页面，或注入恶意JavaScript代码窃取用户会话令牌和登录凭证。
+【WAF/安全设备绕过】前端代理与后端lighttpd对HTTP请求边界解析不一致，允许恶意请求绕过Web应用防火墙(WAF)的检测规则，直接到达后端服务器。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -14497,6 +15284,14 @@
       <c r="J101" s="5" t="inlineStr">
         <is>
           <t>GET /../hello.txt返回200 OK, body='HELLO WORLD!!'。绕过Web根目录限制,泄露上级目录文件。该版本路径规范化存在缺陷。</t>
+        </is>
+      </c>
+      <c r="K101" s="13" t="inlineStr">
+        <is>
+          <t>【敏感文件读取】攻击者可利用lighttpd的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若lighttpd为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -14591,6 +15386,14 @@
           <t>请求包含嵌入CRLF和完整HTTP响应行,可致响应拆分攻击,注入恶意内容/Set-Cookie。7/10组确认。</t>
         </is>
       </c>
+      <c r="K102" s="13" t="inlineStr">
+        <is>
+          <t>【HTTP缓存投毒】攻击者可利用lighttpd的HTTP请求走私/响应分割漏洞，向前端缓存/代理服务器注入恶意HTTP响应，污染缓存内容。后续合法用户请求将收到被篡改的缓存内容，可能导致XSS、恶意重定向或恶意文件下载。
+【会话劫持与凭证窃取】通过HTTP响应头注入，攻击者可构造恶意响应设置Cookie、重定向用户到钓鱼页面，或注入恶意JavaScript代码窃取用户会话令牌和登录凭证。
+【WAF/安全设备绕过】前端代理与后端lighttpd对HTTP请求边界解析不一致，允许恶意请求绕过Web应用防火墙(WAF)的检测规则，直接到达后端服务器。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="260" customHeight="1">
       <c r="A103" s="4" t="inlineStr">
@@ -14714,6 +15517,14 @@
           <t>多个Content-Length头违反RFC 7230。前后端对请求体边界解析不一致导致HTTP走私攻击。10/10组均发现。</t>
         </is>
       </c>
+      <c r="K103" s="13" t="inlineStr">
+        <is>
+          <t>【HTTP缓存投毒】攻击者可利用lighttpd的HTTP请求走私/响应分割漏洞，向前端缓存/代理服务器注入恶意HTTP响应，污染缓存内容。后续合法用户请求将收到被篡改的缓存内容，可能导致XSS、恶意重定向或恶意文件下载。
+【会话劫持与凭证窃取】通过HTTP响应头注入，攻击者可构造恶意响应设置Cookie、重定向用户到钓鱼页面，或注入恶意JavaScript代码窃取用户会话令牌和登录凭证。
+【WAF/安全设备绕过】前端代理与后端lighttpd对HTTP请求边界解析不一致，允许恶意请求绕过Web应用防火墙(WAF)的检测规则，直接到达后端服务器。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="260" customHeight="1">
       <c r="A104" s="5" t="inlineStr">
@@ -14820,6 +15631,14 @@
           <t>GET /../hello.txt返回200 OK, body='HELLO WORLD!!'。绕过Web根目录限制,泄露上级目录文件。该版本路径规范化存在缺陷。</t>
         </is>
       </c>
+      <c r="K104" s="13" t="inlineStr">
+        <is>
+          <t>【敏感文件读取】攻击者可利用lighttpd的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若lighttpd为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="260" customHeight="1">
       <c r="A105" s="4" t="inlineStr">
@@ -14941,6 +15760,14 @@
       <c r="J105" s="4" t="inlineStr">
         <is>
           <t>多个Content-Length头违反RFC 7230。前后端对请求体边界解析不一致导致HTTP走私攻击。10/10组均发现。</t>
+        </is>
+      </c>
+      <c r="K105" s="13" t="inlineStr">
+        <is>
+          <t>【HTTP缓存投毒】攻击者可利用lighttpd的HTTP请求走私/响应分割漏洞，向前端缓存/代理服务器注入恶意HTTP响应，污染缓存内容。后续合法用户请求将收到被篡改的缓存内容，可能导致XSS、恶意重定向或恶意文件下载。
+【会话劫持与凭证窃取】通过HTTP响应头注入，攻击者可构造恶意响应设置Cookie、重定向用户到钓鱼页面，或注入恶意JavaScript代码窃取用户会话令牌和登录凭证。
+【WAF/安全设备绕过】前端代理与后端lighttpd对HTTP请求边界解析不一致，允许恶意请求绕过Web应用防火墙(WAF)的检测规则，直接到达后端服务器。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -15109,6 +15936,14 @@
           <t>GET /../hello.txt返回200 OK, body='HELLO WORLD!!'。绕过Web根目录限制,泄露上级目录文件。该版本路径规范化存在缺陷。</t>
         </is>
       </c>
+      <c r="K106" s="13" t="inlineStr">
+        <is>
+          <t>【敏感文件读取】攻击者可利用lighttpd的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若lighttpd为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="260" customHeight="1">
       <c r="A107" s="5" t="inlineStr">
@@ -15202,6 +16037,14 @@
       <c r="J107" s="5" t="inlineStr">
         <is>
           <t>GET /../hello.txt返回200 OK, body='HELLO WORLD!!'。绕过Web根目录限制,泄露上级目录文件。该版本路径规范化存在缺陷。</t>
+        </is>
+      </c>
+      <c r="K107" s="13" t="inlineStr">
+        <is>
+          <t>【敏感文件读取】攻击者可利用lighttpd的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若lighttpd为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -15451,6 +16294,14 @@
       <c r="J108" s="4" t="inlineStr">
         <is>
           <t>多个Content-Length头违反RFC 7230。前后端对请求体边界解析不一致导致HTTP走私攻击。10/10组均发现。</t>
+        </is>
+      </c>
+      <c r="K108" s="13" t="inlineStr">
+        <is>
+          <t>【HTTP缓存投毒】攻击者可利用lighttpd的HTTP请求走私/响应分割漏洞，向前端缓存/代理服务器注入恶意HTTP响应，污染缓存内容。后续合法用户请求将收到被篡改的缓存内容，可能导致XSS、恶意重定向或恶意文件下载。
+【会话劫持与凭证窃取】通过HTTP响应头注入，攻击者可构造恶意响应设置Cookie、重定向用户到钓鱼页面，或注入恶意JavaScript代码窃取用户会话令牌和登录凭证。
+【WAF/安全设备绕过】前端代理与后端lighttpd对HTTP请求边界解析不一致，允许恶意请求绕过Web应用防火墙(WAF)的检测规则，直接到达后端服务器。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -15684,6 +16535,14 @@
           <t>GET /../hello.txt返回200 OK, body='HELLO WORLD!!'。绕过Web根目录限制,泄露上级目录文件。该版本路径规范化存在缺陷。</t>
         </is>
       </c>
+      <c r="K109" s="13" t="inlineStr">
+        <is>
+          <t>【敏感文件读取】攻击者可利用lighttpd的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若lighttpd为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="260" customHeight="1">
       <c r="A110" s="6" t="inlineStr">
@@ -15777,6 +16636,14 @@
           <t>请求包含嵌入CRLF和完整HTTP响应行,可致响应拆分攻击,注入恶意内容/Set-Cookie。7/10组确认。</t>
         </is>
       </c>
+      <c r="K110" s="13" t="inlineStr">
+        <is>
+          <t>【HTTP缓存投毒】攻击者可利用lighttpd的HTTP请求走私/响应分割漏洞，向前端缓存/代理服务器注入恶意HTTP响应，污染缓存内容。后续合法用户请求将收到被篡改的缓存内容，可能导致XSS、恶意重定向或恶意文件下载。
+【会话劫持与凭证窃取】通过HTTP响应头注入，攻击者可构造恶意响应设置Cookie、重定向用户到钓鱼页面，或注入恶意JavaScript代码窃取用户会话令牌和登录凭证。
+【WAF/安全设备绕过】前端代理与后端lighttpd对HTTP请求边界解析不一致，允许恶意请求绕过Web应用防火墙(WAF)的检测规则，直接到达后端服务器。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="260" customHeight="1">
       <c r="A111" s="5" t="inlineStr">
@@ -15891,6 +16758,14 @@
       <c r="J111" s="5" t="inlineStr">
         <is>
           <t>GET /../hello.txt返回200 OK, body='HELLO WORLD!!'。绕过Web根目录限制,泄露上级目录文件。该版本路径规范化存在缺陷。</t>
+        </is>
+      </c>
+      <c r="K111" s="13" t="inlineStr">
+        <is>
+          <t>【敏感文件读取】攻击者可利用lighttpd的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若lighttpd为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -16128,6 +17003,14 @@
           <t>多个Content-Length头违反RFC 7230。前后端对请求体边界解析不一致导致HTTP走私攻击。10/10组均发现。</t>
         </is>
       </c>
+      <c r="K112" s="13" t="inlineStr">
+        <is>
+          <t>【HTTP缓存投毒】攻击者可利用lighttpd的HTTP请求走私/响应分割漏洞，向前端缓存/代理服务器注入恶意HTTP响应，污染缓存内容。后续合法用户请求将收到被篡改的缓存内容，可能导致XSS、恶意重定向或恶意文件下载。
+【会话劫持与凭证窃取】通过HTTP响应头注入，攻击者可构造恶意响应设置Cookie、重定向用户到钓鱼页面，或注入恶意JavaScript代码窃取用户会话令牌和登录凭证。
+【WAF/安全设备绕过】前端代理与后端lighttpd对HTTP请求边界解析不一致，允许恶意请求绕过Web应用防火墙(WAF)的检测规则，直接到达后端服务器。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="260" customHeight="1">
       <c r="A113" s="4" t="inlineStr">
@@ -16223,6 +17106,14 @@
       <c r="J113" s="4" t="inlineStr">
         <is>
           <t>多个Content-Length头违反RFC 7230。前后端对请求体边界解析不一致导致HTTP走私攻击。10/10组均发现。</t>
+        </is>
+      </c>
+      <c r="K113" s="13" t="inlineStr">
+        <is>
+          <t>【HTTP缓存投毒】攻击者可利用lighttpd的HTTP请求走私/响应分割漏洞，向前端缓存/代理服务器注入恶意HTTP响应，污染缓存内容。后续合法用户请求将收到被篡改的缓存内容，可能导致XSS、恶意重定向或恶意文件下载。
+【会话劫持与凭证窃取】通过HTTP响应头注入，攻击者可构造恶意响应设置Cookie、重定向用户到钓鱼页面，或注入恶意JavaScript代码窃取用户会话令牌和登录凭证。
+【WAF/安全设备绕过】前端代理与后端lighttpd对HTTP请求边界解析不一致，允许恶意请求绕过Web应用防火墙(WAF)的检测规则，直接到达后端服务器。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -16349,6 +17240,14 @@
       <c r="J114" s="5" t="inlineStr">
         <is>
           <t>GET /../hello.txt返回200 OK, body='HELLO WORLD!!'。绕过Web根目录限制,泄露上级目录文件。该版本路径规范化存在缺陷。</t>
+        </is>
+      </c>
+      <c r="K114" s="13" t="inlineStr">
+        <is>
+          <t>【敏感文件读取】攻击者可利用lighttpd的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若lighttpd为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -16658,6 +17557,14 @@
           <t>多个Content-Length头违反RFC 7230。前后端对请求体边界解析不一致导致HTTP走私攻击。10/10组均发现。</t>
         </is>
       </c>
+      <c r="K115" s="13" t="inlineStr">
+        <is>
+          <t>【HTTP缓存投毒】攻击者可利用lighttpd的HTTP请求走私/响应分割漏洞，向前端缓存/代理服务器注入恶意HTTP响应，污染缓存内容。后续合法用户请求将收到被篡改的缓存内容，可能导致XSS、恶意重定向或恶意文件下载。
+【会话劫持与凭证窃取】通过HTTP响应头注入，攻击者可构造恶意响应设置Cookie、重定向用户到钓鱼页面，或注入恶意JavaScript代码窃取用户会话令牌和登录凭证。
+【WAF/安全设备绕过】前端代理与后端lighttpd对HTTP请求边界解析不一致，允许恶意请求绕过Web应用防火墙(WAF)的检测规则，直接到达后端服务器。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="116" ht="260" customHeight="1">
       <c r="A116" s="5" t="inlineStr">
@@ -16955,6 +17862,14 @@
       <c r="J116" s="5" t="inlineStr">
         <is>
           <t>GET /../hello.txt返回200 OK, body='HELLO WORLD!!'。绕过Web根目录限制,泄露上级目录文件。该版本路径规范化存在缺陷。</t>
+        </is>
+      </c>
+      <c r="K116" s="13" t="inlineStr">
+        <is>
+          <t>【敏感文件读取】攻击者可利用lighttpd的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若lighttpd为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -17218,6 +18133,14 @@
           <t>多个Content-Length头违反RFC 7230。前后端对请求体边界解析不一致导致HTTP走私攻击。10/10组均发现。</t>
         </is>
       </c>
+      <c r="K117" s="13" t="inlineStr">
+        <is>
+          <t>【HTTP缓存投毒】攻击者可利用lighttpd的HTTP请求走私/响应分割漏洞，向前端缓存/代理服务器注入恶意HTTP响应，污染缓存内容。后续合法用户请求将收到被篡改的缓存内容，可能导致XSS、恶意重定向或恶意文件下载。
+【会话劫持与凭证窃取】通过HTTP响应头注入，攻击者可构造恶意响应设置Cookie、重定向用户到钓鱼页面，或注入恶意JavaScript代码窃取用户会话令牌和登录凭证。
+【WAF/安全设备绕过】前端代理与后端lighttpd对HTTP请求边界解析不一致，允许恶意请求绕过Web应用防火墙(WAF)的检测规则，直接到达后端服务器。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="260" customHeight="1">
       <c r="A118" s="5" t="inlineStr">
@@ -17309,6 +18232,14 @@
           <t>GET /../hello.txt返回200 OK, body='HELLO WORLD!!'。绕过Web根目录限制,泄露上级目录文件。该版本路径规范化存在缺陷。</t>
         </is>
       </c>
+      <c r="K118" s="13" t="inlineStr">
+        <is>
+          <t>【敏感文件读取】攻击者可利用lighttpd的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若lighttpd为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="260" customHeight="1">
       <c r="A119" s="4" t="inlineStr">
@@ -17403,6 +18334,14 @@
           <t>多个Content-Length头违反RFC 7230。前后端对请求体边界解析不一致导致HTTP走私攻击。10/10组均发现。</t>
         </is>
       </c>
+      <c r="K119" s="13" t="inlineStr">
+        <is>
+          <t>【HTTP缓存投毒】攻击者可利用lighttpd的HTTP请求走私/响应分割漏洞，向前端缓存/代理服务器注入恶意HTTP响应，污染缓存内容。后续合法用户请求将收到被篡改的缓存内容，可能导致XSS、恶意重定向或恶意文件下载。
+【会话劫持与凭证窃取】通过HTTP响应头注入，攻击者可构造恶意响应设置Cookie、重定向用户到钓鱼页面，或注入恶意JavaScript代码窃取用户会话令牌和登录凭证。
+【WAF/安全设备绕过】前端代理与后端lighttpd对HTTP请求边界解析不一致，允许恶意请求绕过Web应用防火墙(WAF)的检测规则，直接到达后端服务器。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="120" ht="260" customHeight="1">
       <c r="A120" s="5" t="inlineStr">
@@ -17510,6 +18449,14 @@
       <c r="J120" s="5" t="inlineStr">
         <is>
           <t>GET /../hello.txt返回200 OK, body='HELLO WORLD!!'。绕过Web根目录限制,泄露上级目录文件。该版本路径规范化存在缺陷。</t>
+        </is>
+      </c>
+      <c r="K120" s="13" t="inlineStr">
+        <is>
+          <t>【敏感文件读取】攻击者可利用lighttpd的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若lighttpd为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -17639,6 +18586,14 @@
           <t>多个Content-Length头违反RFC 7230。前后端对请求体边界解析不一致导致HTTP走私攻击。10/10组均发现。</t>
         </is>
       </c>
+      <c r="K121" s="13" t="inlineStr">
+        <is>
+          <t>【HTTP缓存投毒】攻击者可利用lighttpd的HTTP请求走私/响应分割漏洞，向前端缓存/代理服务器注入恶意HTTP响应，污染缓存内容。后续合法用户请求将收到被篡改的缓存内容，可能导致XSS、恶意重定向或恶意文件下载。
+【会话劫持与凭证窃取】通过HTTP响应头注入，攻击者可构造恶意响应设置Cookie、重定向用户到钓鱼页面，或注入恶意JavaScript代码窃取用户会话令牌和登录凭证。
+【WAF/安全设备绕过】前端代理与后端lighttpd对HTTP请求边界解析不一致，允许恶意请求绕过Web应用防火墙(WAF)的检测规则，直接到达后端服务器。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="260" customHeight="1">
       <c r="A122" s="5" t="inlineStr">
@@ -17744,6 +18699,14 @@
       <c r="J122" s="5" t="inlineStr">
         <is>
           <t>GET /../hello.txt返回200 OK, body='HELLO WORLD!!'。绕过Web根目录限制,泄露上级目录文件。该版本路径规范化存在缺陷。</t>
+        </is>
+      </c>
+      <c r="K122" s="13" t="inlineStr">
+        <is>
+          <t>【敏感文件读取】攻击者可利用lighttpd的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若lighttpd为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -17975,6 +18938,14 @@
           <t>多个Content-Length头违反RFC 7230。前后端对请求体边界解析不一致导致HTTP走私攻击。10/10组均发现。</t>
         </is>
       </c>
+      <c r="K123" s="13" t="inlineStr">
+        <is>
+          <t>【HTTP缓存投毒】攻击者可利用lighttpd的HTTP请求走私/响应分割漏洞，向前端缓存/代理服务器注入恶意HTTP响应，污染缓存内容。后续合法用户请求将收到被篡改的缓存内容，可能导致XSS、恶意重定向或恶意文件下载。
+【会话劫持与凭证窃取】通过HTTP响应头注入，攻击者可构造恶意响应设置Cookie、重定向用户到钓鱼页面，或注入恶意JavaScript代码窃取用户会话令牌和登录凭证。
+【WAF/安全设备绕过】前端代理与后端lighttpd对HTTP请求边界解析不一致，允许恶意请求绕过Web应用防火墙(WAF)的检测规则，直接到达后端服务器。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="124" ht="260" customHeight="1">
       <c r="A124" s="5" t="inlineStr">
@@ -18074,6 +19045,14 @@
       <c r="J124" s="5" t="inlineStr">
         <is>
           <t>GET /../hello.txt返回200 OK, body='HELLO WORLD!!'。绕过Web根目录限制,泄露上级目录文件。该版本路径规范化存在缺陷。</t>
+        </is>
+      </c>
+      <c r="K124" s="13" t="inlineStr">
+        <is>
+          <t>【敏感文件读取】攻击者可利用lighttpd的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若lighttpd为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -18333,6 +19312,14 @@
       <c r="J125" s="4" t="inlineStr">
         <is>
           <t>Content-Length与Transfer-Encoding同时存在,违反RFC 7230。前后端解析差异可致HTTP走私/缓存投毒/请求劫持。</t>
+        </is>
+      </c>
+      <c r="K125" s="13" t="inlineStr">
+        <is>
+          <t>【HTTP缓存投毒】攻击者可利用lighttpd的HTTP请求走私/响应分割漏洞，向前端缓存/代理服务器注入恶意HTTP响应，污染缓存内容。后续合法用户请求将收到被篡改的缓存内容，可能导致XSS、恶意重定向或恶意文件下载。
+【会话劫持与凭证窃取】通过HTTP响应头注入，攻击者可构造恶意响应设置Cookie、重定向用户到钓鱼页面，或注入恶意JavaScript代码窃取用户会话令牌和登录凭证。
+【WAF/安全设备绕过】前端代理与后端lighttpd对HTTP请求边界解析不一致，允许恶意请求绕过Web应用防火墙(WAF)的检测规则，直接到达后端服务器。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -18564,6 +19551,14 @@
       <c r="J126" s="5" t="inlineStr">
         <is>
           <t>GET /../hello.txt返回200 OK, body='HELLO WORLD!!'。绕过Web根目录限制,泄露上级目录文件。该版本路径规范化存在缺陷。</t>
+        </is>
+      </c>
+      <c r="K126" s="13" t="inlineStr">
+        <is>
+          <t>【敏感文件读取】攻击者可利用lighttpd的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若lighttpd为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
